--- a/Exam/gymtrackerpro/lib/service/__tests__/it/user-service/listMembers-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/user-service/listMembers-it-form.xlsx
@@ -321,7 +321,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14325600" cy="2019300"/>
+    <xdr:ext cx="14554200" cy="2757487"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
